--- a/informe/Parametros_Proyecto.xlsx
+++ b/informe/Parametros_Proyecto.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cuestionario_Proyecto" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cuestionario_Proyecto" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cuestionario_Proyecto'!$A$1:$G$33</definedName>
@@ -61,7 +61,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -71,6 +71,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -438,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -488,7 +491,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Año_t</t>
         </is>
@@ -519,7 +522,7 @@
       <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Año_t+x</t>
         </is>
@@ -556,7 +559,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Vida_util_anos</t>
         </is>
@@ -591,7 +594,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Nombre_proyecto</t>
         </is>
@@ -624,7 +627,7 @@
       <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Interesado</t>
         </is>
@@ -657,7 +660,7 @@
       <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Solicitud_No</t>
         </is>
@@ -688,7 +691,7 @@
       <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
@@ -721,7 +724,7 @@
       <c r="G8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Circuito</t>
         </is>
@@ -754,7 +757,7 @@
       <c r="G9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Nivel_tension_conexion</t>
         </is>
@@ -791,7 +794,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Latitud_ficha_EBSA</t>
         </is>
@@ -822,7 +825,7 @@
       <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Longitud_ficha_EBSA</t>
         </is>
@@ -853,7 +856,7 @@
       <c r="G12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Latitud_memoria_calculo</t>
         </is>
@@ -884,7 +887,7 @@
       <c r="G13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Longitud_memoria_calculo</t>
         </is>
@@ -915,7 +918,7 @@
       <c r="G14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Uso_de_cada_coordenada</t>
         </is>
@@ -952,7 +955,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Altura_msnm</t>
         </is>
@@ -983,7 +986,7 @@
       <c r="G16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Potencia_AC_nominal</t>
         </is>
@@ -1014,7 +1017,7 @@
       <c r="G17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Potencia_DC_nominal_STC</t>
         </is>
@@ -1045,7 +1048,7 @@
       <c r="G18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Potencia_DC_real_bifacialidad</t>
         </is>
@@ -1076,7 +1079,7 @@
       <c r="G19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Cantidad_paneles</t>
         </is>
@@ -1107,7 +1110,7 @@
       <c r="G20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Modelo_panel</t>
         </is>
@@ -1140,7 +1143,7 @@
       <c r="G21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Cantidad_inversores</t>
         </is>
@@ -1171,7 +1174,7 @@
       <c r="G22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Modelo_inversor</t>
         </is>
@@ -1204,7 +1207,7 @@
       <c r="G23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Generacion_mensual_proyectada</t>
         </is>
@@ -1235,7 +1238,7 @@
       <c r="G24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Generacion_anual_proyectada</t>
         </is>
@@ -1272,7 +1275,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Transformador_elevacion</t>
         </is>
@@ -1305,7 +1308,7 @@
       <c r="G26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Icc_800V_referencia_memoria</t>
         </is>
@@ -1340,7 +1343,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>If_13.2kV_referencia_memoria</t>
         </is>
@@ -1375,7 +1378,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Certificado_anti_isla</t>
         </is>
@@ -1408,7 +1411,7 @@
       <c r="G29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Capacidad_corte_interruptores_OR</t>
         </is>
@@ -1443,7 +1446,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Elementos_adicionales_PPC_compensacion</t>
         </is>
@@ -1480,7 +1483,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Condiciones_operativas</t>
         </is>
@@ -1517,7 +1520,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Transformador_proyecto_datos</t>
         </is>
@@ -1527,7 +1530,11 @@
           <t>¿Cuáles son el grupo de conexión, impedancias y datos de TAP del transformador propio 'Tr puerto Boyaca 1.25MW'?</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>1250 kVA | 13200 / 800-462 V | Dyn5 | aceite convencional | devanado aluminio | pantalla electrostatica | Factor K1 | DPS incluido | marca Tesla (ref TRF-1250-13200-800-A-K1)</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t>-</t>
@@ -1535,601 +1542,749 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
+          <t>Respondida (Z% asumida, ver fila Impedancia_transformador_asumida)</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>CENTRO DE TRANSFORMACION EVA ELECTRIC 13.2KV C26-688.pdf (cotizacion Ryctel SAS, 22-jul-2026), item 3</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>La cotizacion NO incluye la impedancia de cortocircuito (Z% / ukr): es un documento comercial, no una placa ni un protocolo de pruebas. Grupo de conexion Dyn5 confirmado (dato nuevo). Falta el protocolo de pruebas del fabricante para reemplazar la Z% asumida por el valor real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Escenario_8.2.2_hora</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué hora usar para 8.2.2 cuando min. demanda y max. generación no coinciden?</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Hora 11 (máxima generación real, 564.05 kWh) con su demanda real (7.174 MW)</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Respondida</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Confirmado por el usuario</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Criterio: caso más crítico de inyección solar (riesgo de sobretensión/flujo inverso), más conservador</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Aumento_demanda_t+x</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué incremento de demanda aplicar para el escenario del año t+x?</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>1.04%</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Respondida</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>DOC_REF_EST_1787069892338.pdf, pag. 4</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>EBSA solicita considerar un aumento del 1.04% de la demanda para el ano t+x en esta solicitud</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Vida_util_verificacion</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>30 anos - CONFIRMADO Y APLICADO en todo el LaTeX y Excel (6.2, energia anual, etc.)</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Respondida</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Confirmado por el usuario</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Ya reflejado en todos los documentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Control_tension_PC</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>El inversor Huawei hace de controlador de tension en el punto de conexion (no hay PPC/compensacion adicional), via su rango de factor de potencia ajustable 0.8ad-0.8at</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Respondida</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Confirmado por el usuario</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Analisis_N-1</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>NO se realiza - topologia radial pura sin caminos alternos, no aporta informacion</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Respondida</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Confirmado por el usuario, justificacion tecnica documentada en LaTeX seccion 8.3</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Metodo_calculo_corto_detallado</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Metodologia de cadena de impedancias IEC60909 (equivalente 115kV -&gt; T9 -&gt; lineas 15344 -&gt; transformador propio) documentada en LaTeX seccion 8.1</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Respondida</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Calculo propio, verificado contra PowerFactory</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Resultado: Icc en 800V con red completa = 7.49kA vs 11.2kA de la memoria (sobreestimacion de la memoria por ~1.5x al ignorar la red aguas arriba). Verificacion cruzada en P3: manual 1.14kA vs PowerFactory 1.236kA (~7% diferencia, esperada por aproximacion de suma de magnitudes vs fasores)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Escala_demanda_t_x</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Implementado: constante ESCALA_DEMANDA en Flujo_carga.py (1.0 para ano t, 1.0104 para ano t+x)</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Respondida</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>scripts/Flujo_carga.py</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Cortocircuito.py NO necesita esto (metodo IEC60909 no depende de demanda)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Analisis_8.1_alternativo</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Se propone analisis estadistico de desviacion (CasoBase vs con-GD) ya que EBSA no entrega resultados propios para comparar (10% de CREG no aplicable)</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>El usuario confirma que tiene la ficha tecnica del transformador y la subira despues</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Escenario_8.2.2_hora</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>¿Qué hora usar para 8.2.2 cuando min. demanda y max. generación no coinciden?</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Hora 11 (máxima generación real, 564.05 kWh) con su demanda real (7.174 MW)</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Respondida</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Confirmado por el usuario</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Criterio: caso más crítico de inyección solar (riesgo de sobretensión/flujo inverso), más conservador</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Aumento_demanda_t+x</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>¿Qué incremento de demanda aplicar para el escenario del año t+x?</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>1.04%</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Falta calcular una vez consolidados los resultados de Flujo_carga.py para ambos casos</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>GD_existentes_circuito</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>GD1 (330kVA) en P4_15344, GD2 (330kVA) en P5_15344 - MONTAJE MANUAL por el usuario en PowerFactory (no via script)</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Respondida</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>DOC_REF_EST_1787069892338.pdf pag.4 ('Generadores Distribuidos Conectados: 2')</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Ficha generica acordada: cosphi=1, despacho igual perfil HPS del proyecto propio escalado a 330kW, 0MW en escenario carga pura. Short-Circuit VDE/IEC = 'No Short-Circuit Contribution' (aporte cero) - decision documentada: no hay ficha real disponible (equipo de terceros), es el default de PowerFactory, y es la asuncion mas favorable para la capacidad de corto disponible del proyecto propio. PENDIENTE: usuario monta manualmente, luego se recalculan Flujo_carga.py y Cortocircuito.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Analisis_impacto_GD1_GD2</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Comparar loading/tension en tramo P2-P3 y T9, y margen de Icc en P3/800V vs 10kA, ANTES vs DESPUES de agregar GD1/GD2</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Objetivo: cuantificar cuanto limitan GD1/GD2 la capacidad disponible para el proyecto propio en su punto de conexion. Requiere que el usuario monte GD1/GD2 primero</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>BUG_unidades_Flujo_carga</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>CORREGIDO: los resultados de flujo de carga (ComLdf) en este proyecto vienen en kW/kvar/A, no MW/Mvar/kA. Flujo_carga.py corregido (divide entre 1000). U_kV tambien corregido (antes usaba m:U que resulto ser fase-neutro, ahora se calcula como m:u x uknom)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Respondida</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>scripts/Flujo_carga.py</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>IMPORTANTE: esto retracta el diagnostico anterior de '990 MW en el generador' - el modelo del usuario SIEMPRE estuvo bien, el bug era del script. Verificado cruzando generador, lineas y transformador propio contra fisica esperada. Cortocircuito.py NO tenia este problema (sus variables de corto ya venian en kA nativamente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Confirmacion_fix_corto_generador</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>CONFIRMADO: Ikss=0.7146 kA en la barra propia del generador (Trifasico) tras aplicar Ik3PF=238.2A x3 inversores - coincide casi exacto con lo esperado (714.6A)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Respondida</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>resultados/Resultados_Cortocircuito.xlsx</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>La correccion del aporte a cortocircuito quedo validada con datos reales</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Requisito_equipo_corte_PC</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Segun Anexo 1 del Acuerdo CNO 2121 de 2026: para proyectos 0.25MW&lt;P&lt;1MW (este proyecto: 990kW) se exige en el PC un Interruptor con unidades de disparo, Reconectador o Interruptor de potencia, con capacidad de interrupcion acorde al nivel de cortocircuito de los resultados del estudio de conexion.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Respondida</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Anexo_1_Acuerdo_2121.pdf</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Se conecta con el hallazgo pendiente de 9.2: falta documentar/confirmar el equipo de corte MV (13.2kV) del transformador propio del proyecto - se retoma en el modulo de comprobacion de coordinacion de protecciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Limite_aporte_falla_inversores_regulacion</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Anexo 1 del Acuerdo CNO 2121 de 2026 confirma que los sistemas de generacion basados en inversores no superan 1.1 p.u. de su corriente nominal como aporte a la falla (limitacion de la electronica de potencia, no del ajuste de proteccion).</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Respondida</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Anexo_1_Acuerdo_2121.pdf</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Consistente con la configuracion validada en PowerFactory: Ik3PF=238.2A por inversor ~1.08 p.u. de su corriente nominal - confirma que el aporte de falla del proyecto es pequeno por diseno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Icc_barraje_115kV_SE_referencia_EBSA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>6.002 kA trifasica / 2.622 kA monofasica / X-R=10, en el barraje de 115kV de la S/E Puerto Boyaca (equivalente de red aguas arriba del transformador T9), segun ficha de insumo de EBSA.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>kA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Respondida</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>DOC_REF_EST_1787069892338.pdf (pag. 4)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dato de referencia para el equivalente de red usado en la metodologia de cadena de impedancias de la seccion 8.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Resultado_comprobacion_coordinacion_cabecera</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OK, no requiere reajuste: falla trifasica en P1 15344 pasa de 4112A (sin proyecto) a 4155A (con proyecto, +1.05%); monofasica de 4112A a 4118A (+0.13%). Ambos casos permanecen en zona instantanea (50/50N) con el mismo tiempo de disparo (~0.03s) que ya opera EBSA.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Respondida</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>scripts/Coordinacion_Protecciones.py / Resultados_Coordinacion_Protecciones.xlsx</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Metodologia programada (formula IEC 60255-151 Normal Inverse), reproducible si cambian los resultados de Cortocircuito.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>Impedancia_transformador_asumida</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>Respondida</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>DOC_REF_EST_1787069892338.pdf, pag. 4</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>EBSA solicita considerar un aumento del 1.04% de la demanda para el ano t+x en esta solicitud</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Vida_util_verificacion</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>30 anos - CONFIRMADO Y APLICADO en todo el LaTeX y Excel (6.2, energia anual, etc.)</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Respondida</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Confirmado por el usuario</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Ya reflejado en todos los documentos</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Control_tension_PC</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>El inversor Huawei hace de controlador de tension en el punto de conexion (no hay PPC/compensacion adicional), via su rango de factor de potencia ajustable 0.8ad-0.8at</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Respondida</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Confirmado por el usuario</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Analisis_N-1</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>NO se realiza - topologia radial pura sin caminos alternos, no aporta informacion</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Respondida</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Confirmado por el usuario, justificacion tecnica documentada en LaTeX seccion 8.3</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Metodo_calculo_corto_detallado</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Metodologia de cadena de impedancias IEC60909 (equivalente 115kV -&gt; T9 -&gt; lineas 15344 -&gt; transformador propio) documentada en LaTeX seccion 8.1</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Respondida</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Calculo propio, verificado contra PowerFactory</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Resultado: Icc en 800V con red completa = 7.49kA vs 11.2kA de la memoria (sobreestimacion de la memoria por ~1.5x al ignorar la red aguas arriba). Verificacion cruzada en P3: manual 1.14kA vs PowerFactory 1.236kA (~7% diferencia, esperada por aproximacion de suma de magnitudes vs fasores)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Escala_demanda_t_x</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Implementado: constante ESCALA_DEMANDA en Flujo_carga.py (1.0 para ano t, 1.0104 para ano t+x)</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Respondida</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>scripts/Flujo_carga.py</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Cortocircuito.py NO necesita esto (metodo IEC60909 no depende de demanda)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Analisis_8.1_alternativo</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Se propone analisis estadistico de desviacion (CasoBase vs con-GD) ya que EBSA no entrega resultados propios para comparar (10% de CREG no aplicable)</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Falta calcular una vez consolidados los resultados de Flujo_carga.py para ambos casos</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>GD_existentes_circuito</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>GD1 (330kVA) en P4_15344, GD2 (330kVA) en P5_15344 - MONTAJE MANUAL por el usuario en PowerFactory (no via script)</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>Respondida</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>DOC_REF_EST_1787069892338.pdf pag.4 ('Generadores Distribuidos Conectados: 2')</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Ficha generica acordada: cosphi=1, despacho igual perfil HPS del proyecto propio escalado a 330kW, 0MW en escenario carga pura. Short-Circuit VDE/IEC = 'No Short-Circuit Contribution' (aporte cero) - decision documentada: no hay ficha real disponible (equipo de terceros), es el default de PowerFactory, y es la asuncion mas favorable para la capacidad de corto disponible del proyecto propio. PENDIENTE: usuario monta manualmente, luego se recalculan Flujo_carga.py y Cortocircuito.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Analisis_impacto_GD1_GD2</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Comparar loading/tension en tramo P2-P3 y T9, y margen de Icc en P3/800V vs 10kA, ANTES vs DESPUES de agregar GD1/GD2</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Objetivo: cuantificar cuanto limitan GD1/GD2 la capacidad disponible para el proyecto propio en su punto de conexion. Requiere que el usuario monte GD1/GD2 primero</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>BUG_unidades_Flujo_carga</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>CORREGIDO: los resultados de flujo de carga (ComLdf) en este proyecto vienen en kW/kvar/A, no MW/Mvar/kA. Flujo_carga.py corregido (divide entre 1000). U_kV tambien corregido (antes usaba m:U que resulto ser fase-neutro, ahora se calcula como m:u x uknom)</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Respondida</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>scripts/Flujo_carga.py</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>IMPORTANTE: esto retracta el diagnostico anterior de '990 MW en el generador' - el modelo del usuario SIEMPRE estuvo bien, el bug era del script. Verificado cruzando generador, lineas y transformador propio contra fisica esperada. Cortocircuito.py NO tenia este problema (sus variables de corto ya venian en kA nativamente)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Confirmacion_fix_corto_generador</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>CONFIRMADO: Ikss=0.7146 kA en la barra propia del generador (Trifasico) tras aplicar Ik3PF=238.2A x3 inversores - coincide casi exacto con lo esperado (714.6A)</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>Respondida</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>resultados/Resultados_Cortocircuito.xlsx</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>La correccion del aporte a cortocircuito quedo validada con datos reales</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Requisito_equipo_corte_PC</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Segun Anexo 1 del Acuerdo CNO 2121 de 2026: para proyectos 0.25MW&lt;P&lt;1MW (este proyecto: 990kW) se exige en el PC un Interruptor con unidades de disparo, Reconectador o Interruptor de potencia, con capacidad de interrupcion acorde al nivel de cortocircuito de los resultados del estudio de conexion.</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Respondida</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Anexo_1_Acuerdo_2121.pdf</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Se conecta con el hallazgo pendiente de 9.2: falta documentar/confirmar el equipo de corte MV (13.2kV) del transformador propio del proyecto - se retoma en el modulo de comprobacion de coordinacion de protecciones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Limite_aporte_falla_inversores_regulacion</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Anexo 1 del Acuerdo CNO 2121 de 2026 confirma que los sistemas de generacion basados en inversores no superan 1.1 p.u. de su corriente nominal como aporte a la falla (limitacion de la electronica de potencia, no del ajuste de proteccion).</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Respondida</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Anexo_1_Acuerdo_2121.pdf</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Consistente con la configuracion validada en PowerFactory: Ik3PF=238.2A por inversor ~1.08 p.u. de su corriente nominal - confirma que el aporte de falla del proyecto es pequeno por diseno.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Icc_barraje_115kV_SE_referencia_EBSA</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>6.002 kA trifasica / 2.622 kA monofasica / X-R=10, en el barraje de 115kV de la S/E Puerto Boyaca (equivalente de red aguas arriba del transformador T9), segun ficha de insumo de EBSA.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Respondida (valor tipico asumido, pendiente de confirmar con protocolo de pruebas)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Valor tipico de mercado para transformador de distribucion trifasico de 1250 kVA en aceite, 13.2 kV</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DECISION: a falta del protocolo de pruebas del transformador, se adopta Z=6% como valor tipico. Justificacion: In(BT)=1250kVA/(raiz3 x 800V)=902.1 A; con Z=6% -&gt; Ik''=15.04 kA en la barra de 800 V, que CUMPLE frente a los 25 kA de los aisladores del barraje y los 50 kA (Icu a 1000 V) del interruptor ACB del tablero de BT cotizados. Contexto: el modelo de PowerFactory tenia una Z implicita de 3.91% (daba 23.07 kA, a solo 8% de margen de los 25 kA del barraje) y la memoria de calculo asumio 8.05% (11.2 kA). Ninguno de los dos es tipico para 1250 kVA. ACCION REQUERIDA: fijar uktr=6 en el objeto 'Tr puerto Boyaca 1.25MW' en PowerFactory y volver a correr Cortocircuito.py; los resultados de la barra de 800 V calculados antes de ese cambio no son utilizables.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>Celda_media_tension_PC</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Celda de media tension con RECONECTADOR E INTERRUPTOR CON UNIDADES DE DISPARO (no seccionador fusible)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Respondida (decision del usuario)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Decision del usuario sobre la cotizacion Ryctel C26-688</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>La cotizacion original ofrecia el item 2 como 'CF-17KV-SIE - KIT CELDA DE SECCIONADOR FUSIBLE 17 kV 16 kA' con fusibles tipo HH, que NO cumple el Anexo 1 del Acuerdo CNO 2121 (para 0.25-1 MW exige interruptor con unidades de disparo, reconectador o interruptor de potencia). El usuario decide asumir la celda con reconectador y disparador, opcion que el mismo proveedor ofrece (pag. 1: 'celdas de media tension con rele de proteccion o seccionador fusible'). CON ESTO SE CIERRA la no conformidad de 9.2. PENDIENTE: la cotizacion advierte 'No se incluye parametrizacion del rele (solo aplica para celdas de interruptor)' - hay que contratar/definir esos ajustes, y coordinarlos con el reconectador de cabecera del circuito 15344.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>Secuencia_cero_no_modelada</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Z0 = Z1 en el modelo (secuencia cero no parametrizada)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Pendiente (hallazgo tecnico a corregir)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Verificacion sobre Resultados_Cortocircuito.xlsx</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>HALLAZGO: en el CasoBase, la corriente de falla monofasica es EXACTAMENTE igual a la trifasica en las 15 barras de media tension (ratio Ik1/Ik3 = 1.000000, diferencias solo en el noveno decimal). Eso indica que las impedancias de secuencia cero de lineas y transformadores no estan parametrizadas y PowerFactory esta usando Z0=Z1 por defecto. CONSECUENCIA: las corrientes de falla monofasica NO son utilizables para el diseno de la malla de puesta a tierra, que depende precisamente del camino de secuencia cero. Las fallas TRIFASICAS no estan afectadas por esto y si son utilizables (coordinacion de protecciones).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>Falla_bifasica_en_cero</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Bifasico = 0.0000 kA en las 31 combinaciones barra x caso</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>kA</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Respondida</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>DOC_REF_EST_1787069892338.pdf (pag. 4)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Dato de referencia para el equivalente de red usado en la metodologia de cadena de impedancias de la seccion 8.1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Resultado_comprobacion_coordinacion_cabecera</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>OK, no requiere reajuste: falla trifasica en P1 15344 pasa de 4112A (sin proyecto) a 4155A (con proyecto, +1.05%); monofasica de 4112A a 4118A (+0.13%). Ambos casos permanecen en zona instantanea (50/50N) con el mismo tiempo de disparo (~0.03s) que ya opera EBSA.</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Respondida</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>scripts/Coordinacion_Protecciones.py / Resultados_Coordinacion_Protecciones.xlsx</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Metodologia programada (formula IEC 60255-151 Normal Inverse), reproducible si cambian los resultados de Cortocircuito.py.</t>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Pendiente (defecto de script a corregir)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Verificacion sobre Resultados_Cortocircuito.xlsx</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>DEFECTO: Cortocircuito.py fija iopt_shc='2psc' y lee m:Ikss, pero PowerFactory devuelve 0 para ese tipo de falla (trifasica y monofasica si calculan). Ademas la hoja Resumen marca las 93 combinaciones como Valido=True, por lo que el script no detecta el problema. No afecta la comprobacion de coordinacion (usa trifasica y monofasica) ni el diseno de malla (usa monofasica), pero si deja incompleta la seccion 8.4 de CREG 174.</t>
         </is>
       </c>
     </row>
